--- a/results/cot_inference/mgsm/tiny-aya-fire/summary_majority.xlsx
+++ b/results/cot_inference/mgsm/tiny-aya-fire/summary_majority.xlsx
@@ -460,14 +460,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D2" t="n">
         <v>250</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -486,14 +486,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D3" t="n">
         <v>250</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F3" t="n">

--- a/results/cot_inference/mgsm/tiny-aya-fire/summary_majority.xlsx
+++ b/results/cot_inference/mgsm/tiny-aya-fire/summary_majority.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,14 +460,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D2" t="n">
         <v>250</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -477,26 +477,104 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>te</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D3" t="n">
         <v>250</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>185</v>
+      </c>
+      <c r="D4" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>74.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>151</v>
+      </c>
+      <c r="D5" t="n">
+        <v>250</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>60.4%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>139</v>
+      </c>
+      <c r="D6" t="n">
+        <v>250</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
